--- a/04_Modules/06_Preserve/c_data/06_preserve.xlsx
+++ b/04_Modules/06_Preserve/c_data/06_preserve.xlsx
@@ -5905,7 +5905,7 @@
     <t>corrected</t>
   </si>
   <si>
-    <t>01_Preprocess/03_Quantification/c_data/DAList_corrected.rds</t>
+    <t>01_Preprocess/03_Quantify/c_data/DAList_corrected.rds</t>
   </si>
   <si>
     <t>88b8d60d5a5dd59c66bf102ba6a7c4d5</t>
@@ -5914,7 +5914,7 @@
     <t>modules</t>
   </si>
   <si>
-    <t>04_Network/01_Build_Modules/c_data/modules.rds</t>
+    <t>04_Modules/01_Build/c_data/modules.rds</t>
   </si>
   <si>
     <t>25cd43ced16098e9558525cfe4c1ef5e</t>
